--- a/словари/неопознанное.xlsx
+++ b/словари/неопознанное.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4D257D-779D-414B-A335-84EC0FB72AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81435DF-395E-426C-989C-27894FA4910B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
-    <sheet name="составные" sheetId="2" r:id="rId2"/>
+    <sheet name="Составные_важные" sheetId="3" r:id="rId2"/>
+    <sheet name="составные" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Оборотень — одна из центральных фигур</t>
   </si>
@@ -59,19 +60,56 @@
   </si>
   <si>
     <t>все эти чудеса могли</t>
+  </si>
+  <si>
+    <t>такую духовную метаморфозу</t>
+  </si>
+  <si>
+    <t>такое духовное превращению</t>
+  </si>
+  <si>
+    <t>какую-нибудь диковинную форму</t>
+  </si>
+  <si>
+    <t>какой-нибудь диковинный образ</t>
+  </si>
+  <si>
+    <t>родилась легенда, согласно которой</t>
+  </si>
+  <si>
+    <t>родилось предание, согласно которого</t>
+  </si>
+  <si>
+    <t>волчий аппетит</t>
+  </si>
+  <si>
+    <t>волчье желание поесть</t>
+  </si>
+  <si>
+    <t>Эта классическая гуморальная теория</t>
+  </si>
+  <si>
+    <t>Эта обще-принятре учение жидко-связи</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -94,8 +132,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -376,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.26953125" customWidth="1"/>
@@ -415,14 +454,60 @@
         <v>9</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBE921E2-5E6A-4421-AA5B-78FAD7E19BA2}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="51.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5C0F972-127E-4870-97E1-2BF38EC706C5}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.08984375" customWidth="1"/>
@@ -437,6 +522,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/неопознанное.xlsx
+++ b/словари/неопознанное.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81435DF-395E-426C-989C-27894FA4910B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8B22E5-AE0D-4E85-AA88-E7DA33062C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Оборотень — одна из центральных фигур</t>
   </si>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t>Эта обще-принятре учение жидко-связи</t>
+  </si>
+  <si>
+    <t>«материальную» психологию</t>
+  </si>
+  <si>
+    <t>«плотское» мировоззрение</t>
   </si>
 </sst>
 </file>
@@ -415,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.26953125" customWidth="1"/>
@@ -476,6 +482,14 @@
       </c>
       <c r="B7" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/словари/неопознанное.xlsx
+++ b/словари/неопознанное.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8B22E5-AE0D-4E85-AA88-E7DA33062C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8572DA9-3B90-4E46-83A8-E30E3981DAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
-    <sheet name="Составные_важные" sheetId="3" r:id="rId2"/>
-    <sheet name="составные" sheetId="2" r:id="rId3"/>
+    <sheet name="неизменные" sheetId="4" r:id="rId2"/>
+    <sheet name="Составные_важные" sheetId="3" r:id="rId3"/>
+    <sheet name="составные" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Оборотень — одна из центральных фигур</t>
   </si>
@@ -96,6 +97,30 @@
   </si>
   <si>
     <t>«плотское» мировоззрение</t>
+  </si>
+  <si>
+    <t>истерия, которая теперь выдвигалась</t>
+  </si>
+  <si>
+    <t>сума-сшествие, которое теперь выдвигалось</t>
+  </si>
+  <si>
+    <t>обладал библиотекой, она и близко не могла быть такой обширной</t>
+  </si>
+  <si>
+    <t>обладал книго-хранилищем, оно и близко не могло быть таким обширным</t>
+  </si>
+  <si>
+    <t>возникала еще более мистическая интерпретация</t>
+  </si>
+  <si>
+    <t>возникало еще более чудесное толкование</t>
+  </si>
+  <si>
+    <t>в исходный лисий образ</t>
+  </si>
+  <si>
+    <t>в исходную лисью форму</t>
   </si>
 </sst>
 </file>
@@ -421,10 +446,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="44.26953125" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="57.90625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -492,12 +517,58 @@
         <v>21</v>
       </c>
     </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1444D1FF-4D39-409F-B280-9A70721CA00F}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="75.08984375" customWidth="1"/>
+    <col min="2" max="2" width="78.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBE921E2-5E6A-4421-AA5B-78FAD7E19BA2}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -519,7 +590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5C0F972-127E-4870-97E1-2BF38EC706C5}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/словари/неопознанное.xlsx
+++ b/словари/неопознанное.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8572DA9-3B90-4E46-83A8-E30E3981DAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0505ED-4053-4F82-BB34-61576EE77397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/неопознанное.xlsx
+++ b/словари/неопознанное.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t xml:space="preserve">Оборотень — одна из центральных фигур</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t xml:space="preserve">образ в значительной степени создан </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Легенда о Ромуле и Реме появилась </t>
+  </si>
+  <si>
+    <t xml:space="preserve">предание о Ромуле и Реме появилось </t>
   </si>
   <si>
     <t xml:space="preserve">обладал библиотекой, она и близко не могла быть такой обширной</t>
@@ -425,7 +431,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -534,6 +540,14 @@
       </c>
       <c r="B13" s="2" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -561,18 +575,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -600,10 +614,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -631,18 +645,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/словари/неопознанное.xlsx
+++ b/словари/неопознанное.xlsx
@@ -12,6 +12,7 @@
     <sheet name="неизменные" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Составные_важные" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="составные" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Неизменные_длинные" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t xml:space="preserve">Оборотень — одна из центральных фигур</t>
   </si>
@@ -109,6 +110,18 @@
     <t xml:space="preserve">предание о Ромуле и Реме появилось </t>
   </si>
   <si>
+    <t xml:space="preserve">традиция относительно личности, известной </t>
+  </si>
+  <si>
+    <t xml:space="preserve">устой от-носительно личности, из-вестного</t>
+  </si>
+  <si>
+    <t xml:space="preserve">позднейшей «вервольф-традиции»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">позднейшего «человека-волка устоя»</t>
+  </si>
+  <si>
     <t xml:space="preserve">обладал библиотекой, она и близко не могла быть такой обширной</t>
   </si>
   <si>
@@ -137,6 +150,12 @@
   </si>
   <si>
     <t xml:space="preserve">волчье желание поесть</t>
+  </si>
+  <si>
+    <t xml:space="preserve">этой легенды неизвестно, но считается, что она появилась во второй половине XIX века, как и предыдущая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">этого пре-дания не-известно, но считается, что оно по-явилось во второй половине XIX века, как и пре-дыдущее</t>
   </si>
 </sst>
 </file>
@@ -229,12 +248,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -431,123 +458,139 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -569,24 +612,24 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="75.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="75.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="78.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>29</v>
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>31</v>
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -608,16 +651,16 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="51.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="51.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>33</v>
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -639,24 +682,24 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="33.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="43.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>35</v>
+      <c r="A1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>37</v>
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -668,4 +711,34 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="88.21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;KffffffСтраница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/словари/неопознанное.xlsx
+++ b/словари/неопознанное.xlsx
@@ -1,21 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="6"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FA9F36-30F4-48BA-9E5E-C69BE60593B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Неизменные_короткие" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="неизменные" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Составные_важные" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="составные" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Неизменные_длинные" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
+    <sheet name="неизменные" sheetId="2" r:id="rId2"/>
+    <sheet name="Составные_важные" sheetId="3" r:id="rId3"/>
+    <sheet name="составные" sheetId="4" r:id="rId4"/>
+    <sheet name="Неизменные_длинные" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -24,81 +32,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
-  <si>
-    <t xml:space="preserve">Оборотень — одна из центральных фигур</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оборотень — один из главных образов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">собранный материал, который затем воплотился</t>
-  </si>
-  <si>
-    <t xml:space="preserve">собранное сырьё, которое затем воплотилось</t>
-  </si>
-  <si>
-    <t xml:space="preserve">колдовство и магию опасной</t>
-  </si>
-  <si>
-    <t xml:space="preserve">колдовство и чародейство опасным</t>
-  </si>
-  <si>
-    <t xml:space="preserve">вся эта мистика могла</t>
-  </si>
-  <si>
-    <t xml:space="preserve">все эти чудеса могли</t>
-  </si>
-  <si>
-    <t xml:space="preserve">какую-нибудь диковинную форму</t>
-  </si>
-  <si>
-    <t xml:space="preserve">какой-нибудь диковинный образ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">родилась легенда, согласно которой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">родилось предание, согласно которого</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Эта классическая гуморальная теория</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Эта обще-принятре учение жидко-связи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«материальную» психологию</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«плотское» мировоззрение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">истерия, которая теперь выдвигалась</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сума-сшествие, которое теперь выдвигалось</t>
-  </si>
-  <si>
-    <t xml:space="preserve">возникала еще более мистическая интерпретация</t>
-  </si>
-  <si>
-    <t xml:space="preserve">возникало еще более чудесное толкование</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в исходную лисью форму</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в исходный лисий образ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">мадленской культуры, которая существовала</t>
-  </si>
-  <si>
-    <t xml:space="preserve">мадленского наследия, которое существовало</t>
-  </si>
-  <si>
-    <t xml:space="preserve">фигура в значительной степени создана</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+  <si>
+    <t>Оборотень — одна из центральных фигур</t>
+  </si>
+  <si>
+    <t>Оборотень — один из главных образов</t>
+  </si>
+  <si>
+    <t>собранный материал, который затем воплотился</t>
+  </si>
+  <si>
+    <t>собранное сырьё, которое затем воплотилось</t>
+  </si>
+  <si>
+    <t>колдовство и магию опасной</t>
+  </si>
+  <si>
+    <t>колдовство и чародейство опасным</t>
+  </si>
+  <si>
+    <t>вся эта мистика могла</t>
+  </si>
+  <si>
+    <t>все эти чудеса могли</t>
+  </si>
+  <si>
+    <t>какую-нибудь диковинную форму</t>
+  </si>
+  <si>
+    <t>какой-нибудь диковинный образ</t>
+  </si>
+  <si>
+    <t>родилась легенда, согласно которой</t>
+  </si>
+  <si>
+    <t>родилось предание, согласно которого</t>
+  </si>
+  <si>
+    <t>Эта классическая гуморальная теория</t>
+  </si>
+  <si>
+    <t>Эта обще-принятре учение жидко-связи</t>
+  </si>
+  <si>
+    <t>«материальную» психологию</t>
+  </si>
+  <si>
+    <t>«плотское» мировоззрение</t>
+  </si>
+  <si>
+    <t>истерия, которая теперь выдвигалась</t>
+  </si>
+  <si>
+    <t>сума-сшествие, которое теперь выдвигалось</t>
+  </si>
+  <si>
+    <t>возникала еще более мистическая интерпретация</t>
+  </si>
+  <si>
+    <t>возникало еще более чудесное толкование</t>
+  </si>
+  <si>
+    <t>в исходную лисью форму</t>
+  </si>
+  <si>
+    <t>в исходный лисий образ</t>
+  </si>
+  <si>
+    <t>мадленской культуры, которая существовала</t>
+  </si>
+  <si>
+    <t>мадленского наследия, которое существовало</t>
+  </si>
+  <si>
+    <t>фигура в значительной степени создана</t>
   </si>
   <si>
     <t xml:space="preserve">образ в значительной степени создан </t>
@@ -113,83 +121,74 @@
     <t xml:space="preserve">традиция относительно личности, известной </t>
   </si>
   <si>
-    <t xml:space="preserve">устой от-носительно личности, из-вестного</t>
-  </si>
-  <si>
-    <t xml:space="preserve">позднейшей «вервольф-традиции»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">позднейшего «человека-волка устоя»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обладал библиотекой, она и близко не могла быть такой обширной</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обладал книго-хранилищем, оно и близко не могло быть таким обширным</t>
-  </si>
-  <si>
-    <t xml:space="preserve">такой ожесточенный критицизм считался необходимым</t>
-  </si>
-  <si>
-    <t xml:space="preserve">такая ожесточенная спорность считалась необходимой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">такую духовную метаморфозу</t>
-  </si>
-  <si>
-    <t xml:space="preserve">такое духовное превращению</t>
-  </si>
-  <si>
-    <t xml:space="preserve">собачьей меланхолии</t>
-  </si>
-  <si>
-    <t xml:space="preserve">собачьего уныния</t>
-  </si>
-  <si>
-    <t xml:space="preserve">волчий аппетит</t>
-  </si>
-  <si>
-    <t xml:space="preserve">волчье желание поесть</t>
-  </si>
-  <si>
-    <t xml:space="preserve">этой легенды неизвестно, но считается, что она появилась во второй половине XIX века, как и предыдущая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">этого пре-дания не-известно, но считается, что оно по-явилось во второй половине XIX века, как и пре-дыдущее</t>
+    <t>устой от-носительно личности, из-вестного</t>
+  </si>
+  <si>
+    <t>позднейшей «вервольф-традиции»</t>
+  </si>
+  <si>
+    <t>позднейшего «человека-волка устоя»</t>
+  </si>
+  <si>
+    <t>обладал библиотекой, она и близко не могла быть такой обширной</t>
+  </si>
+  <si>
+    <t>обладал книго-хранилищем, оно и близко не могло быть таким обширным</t>
+  </si>
+  <si>
+    <t>такой ожесточенный критицизм считался необходимым</t>
+  </si>
+  <si>
+    <t>такая ожесточенная спорность считалась необходимой</t>
+  </si>
+  <si>
+    <t>такую духовную метаморфозу</t>
+  </si>
+  <si>
+    <t>такое духовное превращению</t>
+  </si>
+  <si>
+    <t>собачьей меланхолии</t>
+  </si>
+  <si>
+    <t>собачьего уныния</t>
+  </si>
+  <si>
+    <t>волчий аппетит</t>
+  </si>
+  <si>
+    <t>волчье желание поесть</t>
+  </si>
+  <si>
+    <t>этой легенды неизвестно, но считается, что она появилась во второй половине XIX века, как и предыдущая</t>
+  </si>
+  <si>
+    <t>этого пре-дания не-известно, но считается, что оно по-явилось во второй половине XIX века, как и пре-дыдущее</t>
+  </si>
+  <si>
+    <t>Культ этого сильного, ловкого и умного хищника</t>
+  </si>
+  <si>
+    <t>Поклонение этому сильному, ловкому и умному хищнику</t>
+  </si>
+  <si>
+    <t>эта «звериная» культура</t>
+  </si>
+  <si>
+    <t>это «звериное» наследие</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -215,7 +214,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -223,66 +222,35 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -324,12 +292,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -361,7 +329,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -385,7 +353,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -445,27 +413,26 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.91"/>
+    <col min="1" max="1" width="50" style="1" customWidth="1"/>
+    <col min="2" max="2" width="57.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,7 +440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -481,7 +448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -489,7 +456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -497,7 +464,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -505,7 +472,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -513,7 +480,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -521,7 +488,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -529,7 +496,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -537,7 +504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -545,7 +512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -553,7 +520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -561,7 +528,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -569,7 +536,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
@@ -577,7 +544,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -585,7 +552,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>30</v>
       </c>
@@ -593,30 +560,30 @@
         <v>31</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="75.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="78.54"/>
+    <col min="1" max="1" width="75.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="78.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -624,7 +591,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -632,30 +599,30 @@
         <v>35</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="51.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31"/>
+    <col min="1" max="1" width="51.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -664,29 +631,21 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.91"/>
+    <col min="1" max="1" width="33.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="43.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -694,7 +653,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>40</v>
       </c>
@@ -703,28 +662,20 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="88.21"/>
+    <col min="1" max="1" width="88.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>42</v>
       </c>
@@ -733,10 +684,9 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;KffffffСтраница &amp;P</oddFooter>
   </headerFooter>

--- a/словари/неопознанное.xlsx
+++ b/словари/неопознанное.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FA9F36-30F4-48BA-9E5E-C69BE60593B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED9BAA8-5173-4579-BC70-FCB9D9B5122D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
